--- a/data/trans_orig/Q17F_D_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q17F_D_R2-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo de espera en días hasta la consulta en el centro sanitario, en cuartiles (base 2023) en 2007</t>
+          <t>Población según el tiempo de espera en días hasta la consulta en el centro sanitario, en cuartiles (base 2023) en 2007 (tasa de respuesta: 92,28%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6986</t>
+          <t>6961</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20369</t>
+          <t>21004</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6129</t>
+          <t>5978</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19086</t>
+          <t>19442</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17189</t>
+          <t>16757</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36173</t>
+          <t>35235</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2734</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11405</t>
+          <t>12096</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18802</t>
+          <t>18184</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9888</t>
+          <t>10444</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26265</t>
+          <t>25613</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5079</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16866</t>
+          <t>17742</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8168</t>
+          <t>9084</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23007</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17541</t>
+          <t>16128</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35771</t>
+          <t>34552</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73638</t>
+          <t>73175</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91422</t>
+          <t>91341</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>136369</t>
+          <t>136051</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>157589</t>
+          <t>157664</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>216270</t>
+          <t>216642</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>243936</t>
+          <t>244240</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,35%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7235</t>
+          <t>7056</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21479</t>
+          <t>21309</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17203</t>
+          <t>17189</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38545</t>
+          <t>37840</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>27950</t>
+          <t>28154</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>52628</t>
+          <t>53225</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5010</t>
+          <t>4196</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17375</t>
+          <t>16494</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17414</t>
+          <t>18197</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38220</t>
+          <t>37845</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24336</t>
+          <t>25027</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49663</t>
+          <t>49375</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9537</t>
+          <t>8968</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25140</t>
+          <t>24810</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23065</t>
+          <t>22434</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44807</t>
+          <t>44886</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>36871</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>62706</t>
+          <t>63456</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>123709</t>
+          <t>123746</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>145502</t>
+          <t>146235</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>182217</t>
+          <t>183657</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>214729</t>
+          <t>215660</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>312800</t>
+          <t>315584</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>354167</t>
+          <t>355921</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,64%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15971</t>
+          <t>16546</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34602</t>
+          <t>36056</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20246</t>
+          <t>20315</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40252</t>
+          <t>40987</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>40285</t>
+          <t>41676</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>66435</t>
+          <t>67902</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13956</t>
+          <t>13216</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33106</t>
+          <t>31151</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6988</t>
+          <t>6765</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20885</t>
+          <t>20350</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>24128</t>
+          <t>23000</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>46234</t>
+          <t>47377</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18255</t>
+          <t>17774</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15035</t>
+          <t>15549</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31668</t>
+          <t>32564</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23065</t>
+          <t>23605</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43807</t>
+          <t>43671</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>67442</t>
+          <t>67111</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>91647</t>
+          <t>91633</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>116834</t>
+          <t>118141</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>141663</t>
+          <t>142542</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>192769</t>
+          <t>193273</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>227434</t>
+          <t>227420</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>68,94%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16277</t>
+          <t>16109</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33158</t>
+          <t>32690</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26660</t>
+          <t>27377</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51137</t>
+          <t>51669</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>47090</t>
+          <t>46157</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>76536</t>
+          <t>77584</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,88%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>10181</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25162</t>
+          <t>24858</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18156</t>
+          <t>18951</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38300</t>
+          <t>40069</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>31605</t>
+          <t>32188</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>57583</t>
+          <t>58332</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13630</t>
+          <t>13387</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>30281</t>
+          <t>29195</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14982</t>
+          <t>15926</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>32847</t>
+          <t>32640</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>31887</t>
+          <t>32399</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>56689</t>
+          <t>55984</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>108426</t>
+          <t>110966</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>133891</t>
+          <t>134534</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>200200</t>
+          <t>201829</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>230880</t>
+          <t>232591</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>319507</t>
+          <t>319777</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>361047</t>
+          <t>361120</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>73,93%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>59288</t>
+          <t>59039</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>90084</t>
+          <t>90940</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>85481</t>
+          <t>83660</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>123824</t>
+          <t>124655</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>153636</t>
+          <t>153644</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>203874</t>
+          <t>203563</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>39471</t>
+          <t>39498</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>66480</t>
+          <t>67346</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>61221</t>
+          <t>61900</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>95910</t>
+          <t>96555</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>110451</t>
+          <t>109685</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>152006</t>
+          <t>154900</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>44468</t>
+          <t>43740</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>72432</t>
+          <t>72200</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>76114</t>
+          <t>74880</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>110558</t>
+          <t>111501</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>126854</t>
+          <t>126833</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>173179</t>
+          <t>170733</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>400562</t>
+          <t>397595</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>444042</t>
+          <t>444250</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>665630</t>
+          <t>664931</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>722273</t>
+          <t>722375</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1080683</t>
+          <t>1077471</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1151721</t>
+          <t>1150654</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,13%</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo de espera en días hasta la consulta en el centro sanitario, en cuartiles (base 2023) en 2012</t>
+          <t>Población según el tiempo de espera en días hasta la consulta en el centro sanitario, en cuartiles (base 2023) en 2012 (tasa de respuesta: 95,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14793</t>
+          <t>14295</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32717</t>
+          <t>31613</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13468</t>
+          <t>12950</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31387</t>
+          <t>30725</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30820</t>
+          <t>31148</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55326</t>
+          <t>56964</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4587</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17107</t>
+          <t>16907</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7165</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22114</t>
+          <t>21854</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13274</t>
+          <t>13703</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32649</t>
+          <t>33183</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2987</t>
+          <t>2172</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13252</t>
+          <t>12384</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4036</t>
+          <t>3410</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17191</t>
+          <t>17167</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8924</t>
+          <t>8608</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25012</t>
+          <t>24925</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>125581</t>
+          <t>126742</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>147655</t>
+          <t>148750</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>165844</t>
+          <t>166682</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>190976</t>
+          <t>190814</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>302294</t>
+          <t>302089</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>336312</t>
+          <t>334060</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>83,83%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19087</t>
+          <t>17948</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40467</t>
+          <t>38138</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22026</t>
+          <t>22289</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45032</t>
+          <t>43614</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>45831</t>
+          <t>44881</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>75319</t>
+          <t>75293</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11978</t>
+          <t>12069</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29968</t>
+          <t>30616</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26856</t>
+          <t>26939</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51121</t>
+          <t>51933</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43612</t>
+          <t>43155</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72577</t>
+          <t>74078</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17342</t>
+          <t>17923</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38675</t>
+          <t>38826</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35077</t>
+          <t>36686</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63023</t>
+          <t>62470</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>60391</t>
+          <t>59956</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>94971</t>
+          <t>93847</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>132458</t>
+          <t>133951</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>163183</t>
+          <t>162360</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>210984</t>
+          <t>211604</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>248934</t>
+          <t>247724</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>355897</t>
+          <t>352654</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>401342</t>
+          <t>402011</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,46%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14655</t>
+          <t>14290</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34797</t>
+          <t>34244</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15528</t>
+          <t>16712</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35981</t>
+          <t>35242</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35520</t>
+          <t>34253</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>62210</t>
+          <t>62562</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4064</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16793</t>
+          <t>16113</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14763</t>
+          <t>15316</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>36120</t>
+          <t>36176</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>22251</t>
+          <t>23273</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>45890</t>
+          <t>46181</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,3%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9273</t>
+          <t>10702</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27208</t>
+          <t>30810</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27395</t>
+          <t>27656</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51158</t>
+          <t>51947</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43032</t>
+          <t>43824</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72537</t>
+          <t>72996</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,44%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>99754</t>
+          <t>100344</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>126099</t>
+          <t>125984</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>108264</t>
+          <t>108886</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>139502</t>
+          <t>138628</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>219846</t>
+          <t>218929</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>258695</t>
+          <t>258980</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>68,97%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14557</t>
+          <t>13962</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33668</t>
+          <t>34433</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27482</t>
+          <t>27894</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51074</t>
+          <t>52424</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>47755</t>
+          <t>46942</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>78092</t>
+          <t>77932</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9145</t>
+          <t>9490</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13879</t>
+          <t>14493</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33053</t>
+          <t>33989</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17164</t>
+          <t>17256</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>38026</t>
+          <t>37871</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16921</t>
+          <t>17805</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>36687</t>
+          <t>37496</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25624</t>
+          <t>26126</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>47753</t>
+          <t>49735</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>48170</t>
+          <t>48555</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>78384</t>
+          <t>77440</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,2%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>116665</t>
+          <t>117510</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>143123</t>
+          <t>143321</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>212035</t>
+          <t>210848</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>245629</t>
+          <t>246368</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>339519</t>
+          <t>338411</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>379717</t>
+          <t>380226</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,63%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>75938</t>
+          <t>75237</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>113125</t>
+          <t>113769</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>95519</t>
+          <t>97245</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>137801</t>
+          <t>138518</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>184530</t>
+          <t>181779</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>243251</t>
+          <t>238738</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29964</t>
+          <t>30789</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>56002</t>
+          <t>58341</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>77650</t>
+          <t>77425</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>115980</t>
+          <t>118298</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>115283</t>
+          <t>116229</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>162679</t>
+          <t>163498</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>62335</t>
+          <t>61310</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>96916</t>
+          <t>98309</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>111268</t>
+          <t>110678</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>155259</t>
+          <t>155114</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>181408</t>
+          <t>182456</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>240095</t>
+          <t>238613</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,87%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>508468</t>
+          <t>504563</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>559068</t>
+          <t>555395</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>733480</t>
+          <t>730069</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>794469</t>
+          <t>794202</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1256379</t>
+          <t>1253733</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1342729</t>
+          <t>1335496</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,03%</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo de espera en días hasta la consulta en el centro sanitario, en cuartiles (base 2023) en 2016</t>
+          <t>Población según el tiempo de espera en días hasta la consulta en el centro sanitario, en cuartiles (base 2023) en 2016 (tasa de respuesta: 95,3%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14171</t>
+          <t>13449</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31929</t>
+          <t>30118</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20242</t>
+          <t>19264</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40319</t>
+          <t>39427</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36251</t>
+          <t>37099</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63389</t>
+          <t>62712</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,41%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2879</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16127</t>
+          <t>16070</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,82 +7015,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>8,92%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>16851</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>10024</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>26692</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>7,43%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>4,42%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>11,77%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>24492</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>15567</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>36422</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>6,02%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>3,82%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>8,95%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>16851</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>9669</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>25543</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>7,43%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>4,26%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>11,26%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>24492</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>15588</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>36267</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>3,83%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10926</t>
+          <t>10892</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28109</t>
+          <t>27923</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12634</t>
+          <t>12721</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29005</t>
+          <t>29929</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28434</t>
+          <t>26921</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>51595</t>
+          <t>52013</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>119078</t>
+          <t>120976</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>143926</t>
+          <t>144688</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>147141</t>
+          <t>146630</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>173481</t>
+          <t>173583</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>275830</t>
+          <t>275767</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>313075</t>
+          <t>312916</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,88%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13216</t>
+          <t>12931</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32523</t>
+          <t>31936</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17538</t>
+          <t>17651</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39167</t>
+          <t>39125</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>35287</t>
+          <t>33923</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>61926</t>
+          <t>62044</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7194</t>
+          <t>7073</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22809</t>
+          <t>22166</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27714</t>
+          <t>27266</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53306</t>
+          <t>52272</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38680</t>
+          <t>39223</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69744</t>
+          <t>69096</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26972</t>
+          <t>26670</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50589</t>
+          <t>49915</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20297</t>
+          <t>20573</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42444</t>
+          <t>41675</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>50988</t>
+          <t>53307</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>85816</t>
+          <t>85022</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>170337</t>
+          <t>169060</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>200152</t>
+          <t>199662</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>228508</t>
+          <t>228283</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>264108</t>
+          <t>263424</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>409251</t>
+          <t>407072</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>455599</t>
+          <t>453924</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>75,73%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17049</t>
+          <t>17828</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38692</t>
+          <t>40497</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33881</t>
+          <t>35013</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>59797</t>
+          <t>59532</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>59284</t>
+          <t>58393</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>91569</t>
+          <t>90917</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6025</t>
+          <t>5421</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19380</t>
+          <t>18797</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14704</t>
+          <t>15429</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>34175</t>
+          <t>34586</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>24001</t>
+          <t>23973</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>48060</t>
+          <t>47608</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10934</t>
+          <t>11171</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28335</t>
+          <t>28719</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20623</t>
+          <t>20641</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40492</t>
+          <t>41429</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34220</t>
+          <t>35309</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61825</t>
+          <t>61707</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>97819</t>
+          <t>96284</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>123414</t>
+          <t>123240</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>125928</t>
+          <t>123826</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>156247</t>
+          <t>156586</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>230101</t>
+          <t>230999</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>270607</t>
+          <t>272413</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,85%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12648</t>
+          <t>12016</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28491</t>
+          <t>29259</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27620</t>
+          <t>26772</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51707</t>
+          <t>51271</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43261</t>
+          <t>42088</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>72848</t>
+          <t>73279</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10298</t>
+          <t>10050</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25679</t>
+          <t>26477</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18382</t>
+          <t>17776</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39061</t>
+          <t>39718</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>31261</t>
+          <t>33046</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>59411</t>
+          <t>59992</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21365</t>
+          <t>21154</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>41439</t>
+          <t>41113</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>33590</t>
+          <t>32358</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>59812</t>
+          <t>59062</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>58816</t>
+          <t>59653</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>92851</t>
+          <t>92299</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,11%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>131157</t>
+          <t>131718</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>157928</t>
+          <t>158410</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>168914</t>
+          <t>170327</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>204702</t>
+          <t>205155</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>309342</t>
+          <t>308831</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>354790</t>
+          <t>353559</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,39%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>71659</t>
+          <t>69880</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>109319</t>
+          <t>108106</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>118387</t>
+          <t>116471</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>162123</t>
+          <t>161563</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>196733</t>
+          <t>200623</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>258302</t>
+          <t>260124</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>36562</t>
+          <t>35498</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>64435</t>
+          <t>63374</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>85795</t>
+          <t>86988</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>128032</t>
+          <t>126885</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>130866</t>
+          <t>132815</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>182229</t>
+          <t>182930</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>86089</t>
+          <t>86287</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>124100</t>
+          <t>125741</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>102513</t>
+          <t>105590</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>144546</t>
+          <t>147302</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>200390</t>
+          <t>202040</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>257403</t>
+          <t>255272</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>547156</t>
+          <t>549202</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>601055</t>
+          <t>600484</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>706346</t>
+          <t>707331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>771770</t>
+          <t>770334</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1270865</t>
+          <t>1267416</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1353631</t>
+          <t>1352438</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,32%</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo de espera en días hasta la consulta en el centro sanitario, en cuartiles (base 2023) en 2023</t>
+          <t>Población según el tiempo de espera en días hasta la consulta en el centro sanitario, en cuartiles (base 2023) en 2023 (tasa de respuesta: 94,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9964,12 +9964,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6981</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19820</t>
+          <t>18854</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15775</t>
+          <t>15701</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29277</t>
+          <t>29851</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25275</t>
+          <t>26294</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43443</t>
+          <t>44579</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,69%</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17297</t>
+          <t>17727</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33295</t>
+          <t>34720</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24955</t>
+          <t>25477</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40901</t>
+          <t>41068</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46784</t>
+          <t>46687</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69212</t>
+          <t>69656</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,08%</t>
         </is>
       </c>
     </row>
@@ -10190,12 +10190,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12782</t>
+          <t>13046</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26705</t>
+          <t>28244</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26103</t>
+          <t>25919</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43002</t>
+          <t>42632</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>42483</t>
+          <t>42381</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>65803</t>
+          <t>64922</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,31%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42470</t>
+          <t>42767</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61672</t>
+          <t>62014</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60714</t>
+          <t>59957</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80114</t>
+          <t>80746</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>108371</t>
+          <t>108977</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>137757</t>
+          <t>135807</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>50,85%</t>
         </is>
       </c>
     </row>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>16979</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34293</t>
+          <t>35207</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26728</t>
+          <t>27574</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43933</t>
+          <t>44423</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>48184</t>
+          <t>47853</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>72743</t>
+          <t>72744</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10618,7 +10618,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33513</t>
+          <t>33105</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57571</t>
+          <t>56546</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54443</t>
+          <t>53652</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76843</t>
+          <t>76391</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>93624</t>
+          <t>92907</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>125990</t>
+          <t>126967</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,77%</t>
         </is>
       </c>
     </row>
@@ -10759,12 +10759,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25076</t>
+          <t>26413</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46373</t>
+          <t>48027</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10774,12 +10774,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22950</t>
+          <t>22735</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39549</t>
+          <t>40027</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54648</t>
+          <t>50731</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>82770</t>
+          <t>79948</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,27%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>55962</t>
+          <t>54418</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>82623</t>
+          <t>81828</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>61621</t>
+          <t>62605</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>86740</t>
+          <t>86426</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>124413</t>
+          <t>124963</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>160554</t>
+          <t>162115</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>43,12%</t>
         </is>
       </c>
     </row>
@@ -11102,12 +11102,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22546</t>
+          <t>21832</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41939</t>
+          <t>43175</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26181</t>
+          <t>25384</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43203</t>
+          <t>43151</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11152,12 +11152,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>52739</t>
+          <t>53237</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>80011</t>
+          <t>80914</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,37%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33637</t>
+          <t>33514</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>56144</t>
+          <t>55870</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36710</t>
+          <t>37009</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>54697</t>
+          <t>54731</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>75040</t>
+          <t>75968</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>104812</t>
+          <t>104755</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11300,12 +11300,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,31%</t>
         </is>
       </c>
     </row>
@@ -11328,12 +11328,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9356</t>
+          <t>9012</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31431</t>
+          <t>30506</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13780</t>
+          <t>13723</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26299</t>
+          <t>26453</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11378,12 +11378,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26710</t>
+          <t>27077</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50531</t>
+          <t>50264</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11413,12 +11413,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,86%</t>
         </is>
       </c>
     </row>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20517</t>
+          <t>20560</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43526</t>
+          <t>43803</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35808</t>
+          <t>34751</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>55826</t>
+          <t>53335</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11491,12 +11491,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>60980</t>
+          <t>60950</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>92389</t>
+          <t>89985</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>33,77%</t>
         </is>
       </c>
     </row>
@@ -11671,12 +11671,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32332</t>
+          <t>33280</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56127</t>
+          <t>55036</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11686,12 +11686,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35425</t>
+          <t>35102</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>88147</t>
+          <t>88109</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>70193</t>
+          <t>73141</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>131627</t>
+          <t>134127</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>47223</t>
+          <t>47129</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>74265</t>
+          <t>73998</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50877</t>
+          <t>51221</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>129978</t>
+          <t>131043</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>101723</t>
+          <t>100556</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>193022</t>
+          <t>191339</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>34,9%</t>
         </is>
       </c>
     </row>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>27924</t>
+          <t>28412</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>51780</t>
+          <t>52829</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>56993</t>
+          <t>56972</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>218460</t>
+          <t>220209</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>93747</t>
+          <t>94848</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>281465</t>
+          <t>295846</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>53,96%</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46488</t>
+          <t>46442</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>77175</t>
+          <t>77276</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35820</t>
+          <t>31412</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>83927</t>
+          <t>82584</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12060,12 +12060,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>80258</t>
+          <t>80674</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>152256</t>
+          <t>148534</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12095,12 +12095,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,09%</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>92863</t>
+          <t>94283</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>129600</t>
+          <t>131578</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12255,49 +12255,49 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
+          <t>21,7%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>157091</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>117282</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>181987</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>18,45%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>13,77%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
           <t>21,37%</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>157091</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>121737</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>180635</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>18,45%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>14,3%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>21,22%</t>
-        </is>
-      </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>385</t>
@@ -12310,12 +12310,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>226106</t>
+          <t>227705</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>298147</t>
+          <t>297678</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12325,12 +12325,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>150815</t>
+          <t>153314</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>197572</t>
+          <t>195797</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>177904</t>
+          <t>177469</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>273305</t>
+          <t>273066</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>356386</t>
+          <t>357308</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>461926</t>
+          <t>456504</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,31%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>91874</t>
+          <t>92911</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>133440</t>
+          <t>134273</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>139421</t>
+          <t>140061</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>361152</t>
+          <t>378746</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>247339</t>
+          <t>246659</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>539077</t>
+          <t>496571</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>34,06%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>187978</t>
+          <t>185929</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>239103</t>
+          <t>235893</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>192089</t>
+          <t>180516</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>282355</t>
+          <t>281022</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>391247</t>
+          <t>392483</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>506494</t>
+          <t>502505</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,47%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q17F_D_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q17F_D_R2-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6961</t>
+          <t>6892</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21004</t>
+          <t>20446</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5978</t>
+          <t>6535</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19442</t>
+          <t>19441</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16757</t>
+          <t>15909</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35235</t>
+          <t>35286</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12096</t>
+          <t>11488</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5067</t>
+          <t>5741</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18184</t>
+          <t>18451</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10444</t>
+          <t>9672</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25613</t>
+          <t>24415</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>5069</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17742</t>
+          <t>18035</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9084</t>
+          <t>8716</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>23636</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16128</t>
+          <t>15982</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34552</t>
+          <t>34128</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,51%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73175</t>
+          <t>73352</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91341</t>
+          <t>92128</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>136051</t>
+          <t>135508</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>157664</t>
+          <t>157273</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>216642</t>
+          <t>216388</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>244240</t>
+          <t>243725</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,18%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7056</t>
+          <t>7061</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21309</t>
+          <t>21443</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17189</t>
+          <t>16243</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37840</t>
+          <t>36496</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>28154</t>
+          <t>27265</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>53225</t>
+          <t>52250</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4196</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16494</t>
+          <t>16587</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18197</t>
+          <t>17885</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37845</t>
+          <t>38362</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25027</t>
+          <t>25036</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49375</t>
+          <t>47922</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8968</t>
+          <t>9035</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24810</t>
+          <t>24496</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22434</t>
+          <t>23070</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44886</t>
+          <t>45446</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35370</t>
+          <t>36662</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>63456</t>
+          <t>63426</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>123746</t>
+          <t>123574</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>146235</t>
+          <t>144694</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183657</t>
+          <t>184299</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>215660</t>
+          <t>216645</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>315584</t>
+          <t>314039</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>355921</t>
+          <t>353817</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,18%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16546</t>
+          <t>15784</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36056</t>
+          <t>35941</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20315</t>
+          <t>20540</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40987</t>
+          <t>39080</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>41676</t>
+          <t>40657</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>67902</t>
+          <t>68897</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13216</t>
+          <t>12684</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31151</t>
+          <t>30706</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6765</t>
+          <t>7141</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20350</t>
+          <t>21520</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>23000</t>
+          <t>24154</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>47377</t>
+          <t>45962</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>5691</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17774</t>
+          <t>17957</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15549</t>
+          <t>15150</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32564</t>
+          <t>33261</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23605</t>
+          <t>22999</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43671</t>
+          <t>44697</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>67111</t>
+          <t>67729</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>91633</t>
+          <t>91989</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>118141</t>
+          <t>115458</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142542</t>
+          <t>141426</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>193273</t>
+          <t>191903</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>227420</t>
+          <t>227189</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>68,87%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16109</t>
+          <t>16352</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32690</t>
+          <t>32916</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27377</t>
+          <t>26765</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51669</t>
+          <t>51382</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46157</t>
+          <t>47163</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>77584</t>
+          <t>75997</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10181</t>
+          <t>9414</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24858</t>
+          <t>25527</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18951</t>
+          <t>18609</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>40069</t>
+          <t>38280</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>32188</t>
+          <t>32303</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>58332</t>
+          <t>59113</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13387</t>
+          <t>13587</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29195</t>
+          <t>30983</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15926</t>
+          <t>14682</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>32640</t>
+          <t>32548</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>32399</t>
+          <t>32909</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>55984</t>
+          <t>56133</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>110966</t>
+          <t>110935</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>134534</t>
+          <t>135295</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>201829</t>
+          <t>202273</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>232591</t>
+          <t>233874</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>319777</t>
+          <t>320087</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>361120</t>
+          <t>360255</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,75%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>59039</t>
+          <t>58656</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>90940</t>
+          <t>91638</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>83660</t>
+          <t>84711</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>124655</t>
+          <t>124464</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>153644</t>
+          <t>155508</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>203563</t>
+          <t>205889</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>39498</t>
+          <t>38939</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>67346</t>
+          <t>67726</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>61900</t>
+          <t>62156</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>96555</t>
+          <t>95795</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>109685</t>
+          <t>107163</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>154900</t>
+          <t>149683</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>43740</t>
+          <t>43071</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>72200</t>
+          <t>71848</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>74880</t>
+          <t>75987</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>111501</t>
+          <t>112158</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>126833</t>
+          <t>126798</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>170733</t>
+          <t>172058</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>397595</t>
+          <t>399638</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>444250</t>
+          <t>445428</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>664931</t>
+          <t>664215</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>722375</t>
+          <t>721034</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1077471</t>
+          <t>1080960</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1150654</t>
+          <t>1151152</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>73,16%</t>
         </is>
       </c>
     </row>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14295</t>
+          <t>13892</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31613</t>
+          <t>31850</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>13244</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30725</t>
+          <t>30918</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31148</t>
+          <t>30249</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56964</t>
+          <t>54131</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16907</t>
+          <t>16911</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21854</t>
+          <t>21688</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13703</t>
+          <t>13606</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33183</t>
+          <t>32437</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2172</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12384</t>
+          <t>12997</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3410</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17167</t>
+          <t>16254</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8608</t>
+          <t>9129</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>24925</t>
+          <t>25283</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>126742</t>
+          <t>127466</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>148750</t>
+          <t>149129</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>166682</t>
+          <t>166497</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>190814</t>
+          <t>190702</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>302089</t>
+          <t>304239</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>334060</t>
+          <t>334610</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,97%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17948</t>
+          <t>18081</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38138</t>
+          <t>37643</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22289</t>
+          <t>22326</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43614</t>
+          <t>45568</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>44881</t>
+          <t>45524</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>75293</t>
+          <t>74422</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12069</t>
+          <t>12021</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30616</t>
+          <t>31007</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26939</t>
+          <t>27336</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51933</t>
+          <t>51402</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43155</t>
+          <t>44056</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74078</t>
+          <t>74135</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17923</t>
+          <t>17765</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38826</t>
+          <t>39122</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36686</t>
+          <t>36736</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62470</t>
+          <t>63376</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59956</t>
+          <t>59651</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>93847</t>
+          <t>94931</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,64%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>133951</t>
+          <t>133836</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>162360</t>
+          <t>164239</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>211604</t>
+          <t>209406</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>247724</t>
+          <t>247722</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>352654</t>
+          <t>353176</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>402011</t>
+          <t>400922</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,26%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14290</t>
+          <t>14896</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34244</t>
+          <t>33601</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16712</t>
+          <t>16770</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35242</t>
+          <t>37097</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34253</t>
+          <t>35627</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>62562</t>
+          <t>63501</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3941</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16113</t>
+          <t>16209</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15316</t>
+          <t>15109</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>36176</t>
+          <t>35892</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>23273</t>
+          <t>22736</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>46181</t>
+          <t>45164</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10702</t>
+          <t>10291</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30810</t>
+          <t>29864</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27656</t>
+          <t>28547</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51947</t>
+          <t>53269</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43824</t>
+          <t>42249</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72996</t>
+          <t>73131</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,47%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>100344</t>
+          <t>100387</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>125984</t>
+          <t>126809</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>108886</t>
+          <t>107442</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>138628</t>
+          <t>138439</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>218929</t>
+          <t>218718</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>258980</t>
+          <t>257928</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>68,69%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13962</t>
+          <t>14291</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34433</t>
+          <t>33935</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27894</t>
+          <t>27457</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52424</t>
+          <t>50182</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46942</t>
+          <t>47458</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>77932</t>
+          <t>77439</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,2%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9490</t>
+          <t>9372</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,82 +5645,82 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>5,1%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>22259</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>15166</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>33769</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>6,83%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>4,66%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>10,36%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>26351</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>17764</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>37682</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
           <t>5,17%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>22259</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>14493</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>33989</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>6,83%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>4,45%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>10,43%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>26351</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>17256</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>37871</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>5,17%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17805</t>
+          <t>15796</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>37496</t>
+          <t>36072</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>26126</t>
+          <t>25130</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>49735</t>
+          <t>47778</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>48555</t>
+          <t>47572</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>77440</t>
+          <t>77568</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>117510</t>
+          <t>117170</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>143321</t>
+          <t>143580</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>210848</t>
+          <t>214154</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>246368</t>
+          <t>246094</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>338411</t>
+          <t>338865</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>380226</t>
+          <t>379460</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,48%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>75237</t>
+          <t>75691</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>113769</t>
+          <t>113651</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>97245</t>
+          <t>99034</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>138518</t>
+          <t>139149</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>181779</t>
+          <t>183941</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>238738</t>
+          <t>239724</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,93%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30789</t>
+          <t>29560</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>58341</t>
+          <t>57177</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>77425</t>
+          <t>78591</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>118298</t>
+          <t>118001</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>116229</t>
+          <t>114029</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>163498</t>
+          <t>163520</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,7 +6284,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>61310</t>
+          <t>60529</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>98309</t>
+          <t>95752</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>110678</t>
+          <t>109427</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>155114</t>
+          <t>154799</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>182456</t>
+          <t>183562</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>238613</t>
+          <t>238485</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>504563</t>
+          <t>504354</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>555395</t>
+          <t>559782</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,82 +6440,82 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
+          <t>67,61%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>75,04%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>764198</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>732560</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>792770</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>68,96%</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>66,11%</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>71,54%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>1202</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>1296784</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>1254167</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>1332408</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>69,94%</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
           <t>67,64%</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>74,45%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>764198</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>730069</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>794202</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>68,96%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>65,88%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>71,67%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>1202</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>1296784</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>1253733</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>1335496</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>69,94%</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>67,62%</t>
-        </is>
-      </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>71,86%</t>
         </is>
       </c>
     </row>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13449</t>
+          <t>13763</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30118</t>
+          <t>31299</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19264</t>
+          <t>19093</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39427</t>
+          <t>39291</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37099</t>
+          <t>37885</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62712</t>
+          <t>62994</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16070</t>
+          <t>16780</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10024</t>
+          <t>10204</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26692</t>
+          <t>26285</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15567</t>
+          <t>15742</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36422</t>
+          <t>36376</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10892</t>
+          <t>10949</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27923</t>
+          <t>27704</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12721</t>
+          <t>12694</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29929</t>
+          <t>29781</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26921</t>
+          <t>27351</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>52013</t>
+          <t>51494</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>120976</t>
+          <t>119629</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>144688</t>
+          <t>144796</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>146630</t>
+          <t>146873</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>173583</t>
+          <t>174723</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>275767</t>
+          <t>277883</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>312916</t>
+          <t>313247</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,97%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12931</t>
+          <t>13505</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31936</t>
+          <t>32520</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17651</t>
+          <t>18321</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39125</t>
+          <t>39397</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>33923</t>
+          <t>35073</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>62044</t>
+          <t>61744</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7073</t>
+          <t>7072</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22166</t>
+          <t>22484</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27266</t>
+          <t>27119</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52272</t>
+          <t>51287</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39223</t>
+          <t>39236</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69096</t>
+          <t>67458</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26670</t>
+          <t>26536</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49915</t>
+          <t>49837</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20573</t>
+          <t>19526</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41675</t>
+          <t>41496</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53307</t>
+          <t>52781</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>85022</t>
+          <t>87386</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>169060</t>
+          <t>170790</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>199662</t>
+          <t>199303</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>228283</t>
+          <t>229429</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>263424</t>
+          <t>263583</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>407072</t>
+          <t>408332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>453924</t>
+          <t>454853</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,89%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17828</t>
+          <t>18051</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40497</t>
+          <t>40094</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35013</t>
+          <t>34513</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>59532</t>
+          <t>60358</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>58393</t>
+          <t>59244</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>90917</t>
+          <t>92364</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5421</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18797</t>
+          <t>19223</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15429</t>
+          <t>14609</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>34586</t>
+          <t>33552</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>23973</t>
+          <t>24205</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>47608</t>
+          <t>47351</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11171</t>
+          <t>10800</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28719</t>
+          <t>28230</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20641</t>
+          <t>20705</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41429</t>
+          <t>40446</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35309</t>
+          <t>35361</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61707</t>
+          <t>62559</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,35%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>96284</t>
+          <t>96008</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>123240</t>
+          <t>123107</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>123826</t>
+          <t>125258</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>156586</t>
+          <t>155973</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>230999</t>
+          <t>231349</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>272413</t>
+          <t>270353</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>66,35%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12016</t>
+          <t>11473</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29259</t>
+          <t>27969</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26772</t>
+          <t>27286</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51271</t>
+          <t>52171</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42088</t>
+          <t>43469</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>73279</t>
+          <t>72635</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10050</t>
+          <t>10379</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26477</t>
+          <t>26592</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17776</t>
+          <t>17624</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39718</t>
+          <t>39060</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>33046</t>
+          <t>32288</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>59992</t>
+          <t>58972</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21154</t>
+          <t>21644</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>41113</t>
+          <t>41537</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>32358</t>
+          <t>33695</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>59062</t>
+          <t>58894</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>59653</t>
+          <t>60207</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>92299</t>
+          <t>92193</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>131718</t>
+          <t>132124</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>158410</t>
+          <t>158062</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>170327</t>
+          <t>167255</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>205155</t>
+          <t>203325</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>308831</t>
+          <t>310480</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>353559</t>
+          <t>354852</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>69,64%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>69880</t>
+          <t>70285</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>108106</t>
+          <t>107819</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>116471</t>
+          <t>117428</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>161563</t>
+          <t>164343</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>200623</t>
+          <t>198395</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>260124</t>
+          <t>257585</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>35498</t>
+          <t>36687</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>63374</t>
+          <t>64365</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>86988</t>
+          <t>88593</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>126885</t>
+          <t>129265</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>132815</t>
+          <t>132423</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>182930</t>
+          <t>181705</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>86287</t>
+          <t>86880</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>125741</t>
+          <t>123991</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>105590</t>
+          <t>103876</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>147302</t>
+          <t>146794</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>202040</t>
+          <t>202692</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>255272</t>
+          <t>258262</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>549202</t>
+          <t>546112</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>600484</t>
+          <t>600323</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>707331</t>
+          <t>704569</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>770334</t>
+          <t>768511</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1267416</t>
+          <t>1275170</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1352438</t>
+          <t>1358815</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,65%</t>
         </is>
       </c>
     </row>
@@ -9959,32 +9959,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12262</t>
+          <t>13326</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>7442</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18854</t>
+          <t>21944</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9994,32 +9994,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>21664</t>
+          <t>23790</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15701</t>
+          <t>17387</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29851</t>
+          <t>32047</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10029,32 +10029,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>33926</t>
+          <t>37116</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26294</t>
+          <t>28225</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44579</t>
+          <t>46868</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -10072,32 +10072,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25003</t>
+          <t>26620</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17727</t>
+          <t>18287</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34720</t>
+          <t>36112</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10107,32 +10107,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>32495</t>
+          <t>34654</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25477</t>
+          <t>27374</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41068</t>
+          <t>44268</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10142,32 +10142,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>57498</t>
+          <t>61274</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46687</t>
+          <t>50425</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69656</t>
+          <t>73570</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,89%</t>
         </is>
       </c>
     </row>
@@ -10185,32 +10185,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19453</t>
+          <t>21244</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13046</t>
+          <t>13673</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28244</t>
+          <t>29778</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10220,32 +10220,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>33758</t>
+          <t>36732</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25919</t>
+          <t>29365</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>42632</t>
+          <t>46114</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10255,32 +10255,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>53211</t>
+          <t>57976</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>42381</t>
+          <t>47184</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>64922</t>
+          <t>70520</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -10298,32 +10298,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>52068</t>
+          <t>53919</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42767</t>
+          <t>43627</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62014</t>
+          <t>65063</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10333,32 +10333,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>70376</t>
+          <t>73826</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59957</t>
+          <t>63616</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80746</t>
+          <t>84542</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10368,32 +10368,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>122444</t>
+          <t>127744</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>108977</t>
+          <t>111571</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>135807</t>
+          <t>142937</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,31%</t>
         </is>
       </c>
     </row>
@@ -10411,17 +10411,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>108786</t>
+          <t>115109</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>108786</t>
+          <t>115109</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>108786</t>
+          <t>115109</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10446,17 +10446,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>158293</t>
+          <t>169002</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>158293</t>
+          <t>169002</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>158293</t>
+          <t>169002</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10481,17 +10481,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>267079</t>
+          <t>284110</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>267079</t>
+          <t>284110</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>267079</t>
+          <t>284110</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10528,32 +10528,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24360</t>
+          <t>28497</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16979</t>
+          <t>19692</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35207</t>
+          <t>40192</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10563,32 +10563,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34910</t>
+          <t>38839</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27574</t>
+          <t>30505</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>44423</t>
+          <t>49154</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10598,32 +10598,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>59270</t>
+          <t>67336</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>47853</t>
+          <t>55579</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>72744</t>
+          <t>83259</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -10641,32 +10641,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>44145</t>
+          <t>51272</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33105</t>
+          <t>40040</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56546</t>
+          <t>66962</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10676,32 +10676,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>64861</t>
+          <t>74785</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53652</t>
+          <t>63268</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76391</t>
+          <t>87595</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10711,32 +10711,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>109007</t>
+          <t>126056</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>92907</t>
+          <t>107747</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>126967</t>
+          <t>144172</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>34,04%</t>
         </is>
       </c>
     </row>
@@ -10754,32 +10754,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35594</t>
+          <t>38077</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26413</t>
+          <t>27200</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48027</t>
+          <t>50292</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10789,32 +10789,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30565</t>
+          <t>35501</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22735</t>
+          <t>26798</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40027</t>
+          <t>46514</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10824,32 +10824,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>66159</t>
+          <t>73578</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>50731</t>
+          <t>58006</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>79948</t>
+          <t>89086</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -10867,32 +10867,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>68094</t>
+          <t>73601</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54418</t>
+          <t>58448</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>81828</t>
+          <t>88912</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10902,32 +10902,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>73423</t>
+          <t>82958</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62605</t>
+          <t>69685</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>86426</t>
+          <t>98057</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10937,32 +10937,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>141517</t>
+          <t>156558</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>124963</t>
+          <t>136514</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>162115</t>
+          <t>176543</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>41,68%</t>
         </is>
       </c>
     </row>
@@ -10980,17 +10980,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>172193</t>
+          <t>191447</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>172193</t>
+          <t>191447</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>172193</t>
+          <t>191447</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11015,17 +11015,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>203760</t>
+          <t>232083</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>203760</t>
+          <t>232083</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>203760</t>
+          <t>232083</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11050,17 +11050,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>375953</t>
+          <t>423529</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>375953</t>
+          <t>423529</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>375953</t>
+          <t>423529</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11097,32 +11097,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>31512</t>
+          <t>33269</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21832</t>
+          <t>23468</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43175</t>
+          <t>44327</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11132,32 +11132,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>34076</t>
+          <t>41068</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25384</t>
+          <t>31952</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43151</t>
+          <t>51540</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11167,32 +11167,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>65587</t>
+          <t>74338</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53237</t>
+          <t>60658</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>80914</t>
+          <t>88824</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>29,09%</t>
         </is>
       </c>
     </row>
@@ -11210,32 +11210,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44600</t>
+          <t>47322</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33514</t>
+          <t>36619</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55870</t>
+          <t>59249</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11245,32 +11245,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>45271</t>
+          <t>55305</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37009</t>
+          <t>45398</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>54731</t>
+          <t>66752</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11280,32 +11280,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>89871</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>75968</t>
+          <t>86716</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>104755</t>
+          <t>118563</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>38,83%</t>
         </is>
       </c>
     </row>
@@ -11323,32 +11323,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>17202</t>
+          <t>17933</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9012</t>
+          <t>10121</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30506</t>
+          <t>29801</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11358,32 +11358,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>19720</t>
+          <t>22217</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13723</t>
+          <t>15979</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26453</t>
+          <t>31216</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11393,32 +11393,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>36921</t>
+          <t>40150</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27077</t>
+          <t>29763</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50264</t>
+          <t>54768</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -11436,32 +11436,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>30043</t>
+          <t>36115</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20560</t>
+          <t>26684</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43803</t>
+          <t>47957</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11471,32 +11471,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>44031</t>
+          <t>52091</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34751</t>
+          <t>41991</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53335</t>
+          <t>64440</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11506,32 +11506,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>74074</t>
+          <t>88206</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>60950</t>
+          <t>74215</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>89985</t>
+          <t>105397</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>34,52%</t>
         </is>
       </c>
     </row>
@@ -11549,17 +11549,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>123357</t>
+          <t>134639</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>123357</t>
+          <t>134639</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>123357</t>
+          <t>134639</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11584,17 +11584,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>143097</t>
+          <t>170681</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>143097</t>
+          <t>170681</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>143097</t>
+          <t>170681</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11619,17 +11619,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>266453</t>
+          <t>305320</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>266453</t>
+          <t>305320</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>266453</t>
+          <t>305320</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11666,32 +11666,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>42520</t>
+          <t>45873</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33280</t>
+          <t>35950</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55036</t>
+          <t>59446</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11701,32 +11701,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>66441</t>
+          <t>74585</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35102</t>
+          <t>62249</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>88109</t>
+          <t>88141</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11736,32 +11736,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>108961</t>
+          <t>120458</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>73141</t>
+          <t>103126</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>134127</t>
+          <t>138701</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>27,07%</t>
         </is>
       </c>
     </row>
@@ -11779,32 +11779,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>60649</t>
+          <t>63154</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>47129</t>
+          <t>49755</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>73998</t>
+          <t>76746</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11814,32 +11814,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>98723</t>
+          <t>102928</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51221</t>
+          <t>88342</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>131043</t>
+          <t>117494</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11849,32 +11849,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>159373</t>
+          <t>166082</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>100556</t>
+          <t>147046</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>191339</t>
+          <t>183672</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,85%</t>
         </is>
       </c>
     </row>
@@ -11892,32 +11892,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38440</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>28412</t>
+          <t>29098</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>52829</t>
+          <t>52344</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11927,32 +11927,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>119321</t>
+          <t>59003</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>56972</t>
+          <t>47348</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>220209</t>
+          <t>72724</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11962,32 +11962,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>157722</t>
+          <t>97442</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>94848</t>
+          <t>82418</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>295846</t>
+          <t>114939</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -12005,32 +12005,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>60466</t>
+          <t>63043</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46442</t>
+          <t>48757</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>77276</t>
+          <t>76983</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12040,32 +12040,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>61788</t>
+          <t>65265</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31412</t>
+          <t>51080</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>82584</t>
+          <t>78726</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12075,32 +12075,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>122253</t>
+          <t>128308</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>80674</t>
+          <t>110384</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>148534</t>
+          <t>149192</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>29,12%</t>
         </is>
       </c>
     </row>
@@ -12118,17 +12118,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>202036</t>
+          <t>210510</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>202036</t>
+          <t>210510</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>202036</t>
+          <t>210510</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12153,17 +12153,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>346273</t>
+          <t>301781</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>346273</t>
+          <t>301781</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>346273</t>
+          <t>301781</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12188,17 +12188,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>548309</t>
+          <t>512291</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>548309</t>
+          <t>512291</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>548309</t>
+          <t>512291</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12235,32 +12235,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>110653</t>
+          <t>120965</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>94283</t>
+          <t>102826</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>131578</t>
+          <t>142922</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12270,32 +12270,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>157091</t>
+          <t>178282</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>117282</t>
+          <t>160135</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>181987</t>
+          <t>200627</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12305,32 +12305,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>267744</t>
+          <t>299248</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>227705</t>
+          <t>272816</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>297678</t>
+          <t>329167</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>21,58%</t>
         </is>
       </c>
     </row>
@@ -12348,32 +12348,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>174398</t>
+          <t>188368</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>153314</t>
+          <t>165837</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>195797</t>
+          <t>213198</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12383,32 +12383,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>241351</t>
+          <t>267672</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>177469</t>
+          <t>244375</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>273066</t>
+          <t>293647</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12418,32 +12418,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>415749</t>
+          <t>456040</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>357308</t>
+          <t>421598</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>456504</t>
+          <t>488765</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>32,04%</t>
         </is>
       </c>
     </row>
@@ -12461,32 +12461,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>110650</t>
+          <t>115693</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>92911</t>
+          <t>96400</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>134273</t>
+          <t>138081</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12496,32 +12496,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>203364</t>
+          <t>153453</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>140061</t>
+          <t>133619</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>378746</t>
+          <t>172930</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12531,32 +12531,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>314014</t>
+          <t>269147</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>246659</t>
+          <t>241851</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>496571</t>
+          <t>297008</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>19,47%</t>
         </is>
       </c>
     </row>
@@ -12574,32 +12574,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>210671</t>
+          <t>226677</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>185929</t>
+          <t>201204</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>235893</t>
+          <t>252849</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12609,32 +12609,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>249617</t>
+          <t>274140</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>180516</t>
+          <t>250349</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>281022</t>
+          <t>299421</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12644,32 +12644,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>460289</t>
+          <t>500817</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>392483</t>
+          <t>469137</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>502505</t>
+          <t>542669</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>35,58%</t>
         </is>
       </c>
     </row>
@@ -12687,17 +12687,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>606372</t>
+          <t>651704</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>606372</t>
+          <t>651704</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>606372</t>
+          <t>651704</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12722,17 +12722,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>851423</t>
+          <t>873547</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>851423</t>
+          <t>873547</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>851423</t>
+          <t>873547</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12757,17 +12757,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1457795</t>
+          <t>1525251</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1457795</t>
+          <t>1525251</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1457795</t>
+          <t>1525251</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
